--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D2CE1A-1F8A-42FA-9847-0003FF1F0846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85C5E911-1330-475D-B0FB-2C0DB469565D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1430" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="47">
   <si>
     <t>日付</t>
   </si>
@@ -1247,392 +1247,212 @@
       <c r="E32" s="5"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A33" s="6">
-        <v>45901</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C33" s="7">
-        <v>5876172</v>
-      </c>
+      <c r="A33" s="6"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A34" s="6">
-        <v>45902</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="7">
-        <v>1816205</v>
-      </c>
+      <c r="A34" s="6"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="5"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A35" s="6">
-        <v>45903</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C35" s="7">
-        <v>13025471</v>
-      </c>
+      <c r="A35" s="6"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="5"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A36" s="6">
-        <v>45904</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C36" s="7">
-        <v>806267</v>
-      </c>
+      <c r="A36" s="6"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A37" s="6">
-        <v>45905</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37" s="7">
-        <v>1702611</v>
-      </c>
+      <c r="A37" s="6"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A38" s="6">
-        <v>45906</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="7">
-        <v>1095487</v>
-      </c>
+      <c r="A38" s="6"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A39" s="6">
-        <v>45907</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C39" s="7">
-        <v>2980126</v>
-      </c>
+      <c r="A39" s="6"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A40" s="6">
-        <v>45908</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="7">
-        <v>2053346</v>
-      </c>
+      <c r="A40" s="6"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A41" s="6">
-        <v>45909</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="7">
-        <v>1689816</v>
-      </c>
+      <c r="A41" s="6"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A42" s="6">
-        <v>45910</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C42" s="7">
-        <v>1174843</v>
-      </c>
+      <c r="A42" s="6"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A43" s="6">
-        <v>45911</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C43" s="7">
-        <v>1146686</v>
-      </c>
+      <c r="A43" s="6"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A44" s="6">
-        <v>45912</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C44" s="7">
-        <v>829634</v>
-      </c>
+      <c r="A44" s="6"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A45" s="6">
-        <v>45913</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" s="7">
-        <v>12629003</v>
-      </c>
+      <c r="A45" s="6"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A46" s="6">
-        <v>45914</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C46" s="7">
-        <v>2142969</v>
-      </c>
+      <c r="A46" s="6"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="6">
-        <v>45915</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C47" s="7">
-        <v>1652380</v>
-      </c>
+      <c r="A47" s="6"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="6">
-        <v>45916</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C48" s="7">
-        <v>1084704</v>
-      </c>
+      <c r="A48" s="6"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A49" s="6">
-        <v>45917</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C49" s="7">
-        <v>1004605</v>
-      </c>
+      <c r="A49" s="6"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A50" s="6">
-        <v>45918</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C50" s="7">
-        <v>1060426</v>
-      </c>
+      <c r="A50" s="6"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="7"/>
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A51" s="6">
-        <v>45919</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C51" s="7">
-        <v>623483</v>
-      </c>
+      <c r="A51" s="6"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="7"/>
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A52" s="6">
-        <v>45920</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C52" s="7">
-        <v>1897026</v>
-      </c>
+      <c r="A52" s="6"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="7"/>
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A53" s="6">
-        <v>45921</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C53" s="7">
-        <v>2391636</v>
-      </c>
+      <c r="A53" s="6"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="7"/>
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A54" s="6">
-        <v>45922</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C54" s="7">
-        <v>1410917</v>
-      </c>
+      <c r="A54" s="6"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A55" s="6">
-        <v>45923</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C55" s="7">
-        <v>16532166</v>
-      </c>
+      <c r="A55" s="6"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="7"/>
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A56" s="6">
-        <v>45924</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C56" s="7">
-        <v>741793</v>
-      </c>
+      <c r="A56" s="6"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="7"/>
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A57" s="6">
-        <v>45925</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C57" s="7">
-        <v>1952437</v>
-      </c>
+      <c r="A57" s="6"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="7"/>
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A58" s="6">
-        <v>45926</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C58" s="7">
-        <v>898457</v>
-      </c>
+      <c r="A58" s="6"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="7"/>
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A59" s="6">
-        <v>45927</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C59" s="7">
-        <v>1892478</v>
-      </c>
+      <c r="A59" s="6"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="7"/>
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A60" s="6">
-        <v>45928</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C60" s="7">
-        <v>2958822</v>
-      </c>
+      <c r="A60" s="6"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="7"/>
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A61" s="6">
-        <v>45929</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C61" s="7">
-        <v>1120533</v>
-      </c>
+      <c r="A61" s="6"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A62" s="6">
-        <v>45930</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C62" s="7">
-        <v>1286295</v>
-      </c>
+      <c r="A62" s="6"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="E62" s="5"/>
     </row>

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,7 +12,7 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1721</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,32 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,14 +242,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,7 +286,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -248,23 +293,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,10 +317,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -293,55 +333,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,85 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,19 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,54 +572,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -634,11 +586,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,154 +626,196 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1764"/>
+  <dimension ref="A1:E1721"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23168,254 +23168,34 @@
       </c>
       <c r="D1719" s="7"/>
     </row>
-    <row r="1720" spans="1:4">
-      <c r="A1720" s="4"/>
-      <c r="B1720" s="5"/>
-      <c r="C1720" s="7"/>
-      <c r="D1720" s="7"/>
-    </row>
-    <row r="1721" spans="1:4">
-      <c r="A1721" s="4"/>
-      <c r="B1721" s="5"/>
-      <c r="C1721" s="7"/>
-      <c r="D1721" s="7"/>
-    </row>
-    <row r="1722" spans="1:4">
-      <c r="A1722" s="4"/>
-      <c r="B1722" s="5"/>
-      <c r="C1722" s="7"/>
-      <c r="D1722" s="7"/>
-    </row>
-    <row r="1723" spans="1:4">
-      <c r="A1723" s="4"/>
-      <c r="B1723" s="5"/>
-      <c r="C1723" s="7"/>
-      <c r="D1723" s="7"/>
-    </row>
-    <row r="1724" spans="1:4">
-      <c r="A1724" s="4"/>
-      <c r="B1724" s="5"/>
-      <c r="C1724" s="7"/>
-      <c r="D1724" s="7"/>
-    </row>
-    <row r="1725" spans="1:4">
-      <c r="A1725" s="4"/>
-      <c r="B1725" s="5"/>
-      <c r="C1725" s="7"/>
-      <c r="D1725" s="7"/>
-    </row>
-    <row r="1726" spans="1:4">
-      <c r="A1726" s="4"/>
-      <c r="B1726" s="5"/>
-      <c r="C1726" s="7"/>
-      <c r="D1726" s="7"/>
-    </row>
-    <row r="1727" spans="1:4">
-      <c r="A1727" s="4"/>
-      <c r="B1727" s="5"/>
-      <c r="C1727" s="7"/>
-      <c r="D1727" s="7"/>
-    </row>
-    <row r="1728" spans="1:4">
-      <c r="A1728" s="4"/>
-      <c r="B1728" s="5"/>
-      <c r="C1728" s="7"/>
-      <c r="D1728" s="7"/>
-    </row>
-    <row r="1729" spans="1:4">
-      <c r="A1729" s="4"/>
-      <c r="B1729" s="5"/>
-      <c r="C1729" s="7"/>
-      <c r="D1729" s="7"/>
-    </row>
-    <row r="1730" spans="1:4">
-      <c r="A1730" s="4"/>
-      <c r="B1730" s="5"/>
-      <c r="C1730" s="7"/>
-      <c r="D1730" s="7"/>
-    </row>
-    <row r="1731" spans="3:4">
-      <c r="C1731" s="7"/>
-      <c r="D1731" s="7"/>
-    </row>
-    <row r="1732" spans="1:4">
-      <c r="A1732" s="4"/>
-      <c r="B1732" s="5"/>
-      <c r="C1732" s="7"/>
-      <c r="D1732" s="7"/>
-    </row>
-    <row r="1733" spans="1:4">
-      <c r="A1733" s="4"/>
-      <c r="B1733" s="5"/>
-      <c r="C1733" s="7"/>
-      <c r="D1733" s="7"/>
-    </row>
-    <row r="1734" spans="1:4">
-      <c r="A1734" s="4"/>
-      <c r="B1734" s="5"/>
-      <c r="C1734" s="7"/>
-      <c r="D1734" s="7"/>
-    </row>
-    <row r="1735" spans="1:4">
-      <c r="A1735" s="4"/>
-      <c r="B1735" s="5"/>
-      <c r="C1735" s="7"/>
-      <c r="D1735" s="7"/>
-    </row>
-    <row r="1736" spans="1:4">
-      <c r="A1736" s="4"/>
-      <c r="B1736" s="5"/>
-      <c r="C1736" s="7"/>
-      <c r="D1736" s="7"/>
-    </row>
-    <row r="1737" spans="1:4">
-      <c r="A1737" s="4"/>
-      <c r="B1737" s="5"/>
-      <c r="C1737" s="7"/>
-      <c r="D1737" s="7"/>
-    </row>
-    <row r="1738" spans="1:4">
-      <c r="A1738" s="4"/>
-      <c r="B1738" s="5"/>
-      <c r="C1738" s="7"/>
-      <c r="D1738" s="7"/>
-    </row>
-    <row r="1739" spans="1:4">
-      <c r="A1739" s="4"/>
-      <c r="B1739" s="5"/>
-      <c r="C1739" s="7"/>
-      <c r="D1739" s="7"/>
-    </row>
-    <row r="1740" spans="1:4">
-      <c r="A1740" s="4"/>
-      <c r="B1740" s="5"/>
-      <c r="C1740" s="7"/>
-      <c r="D1740" s="7"/>
-    </row>
-    <row r="1741" spans="1:4">
-      <c r="A1741" s="4"/>
-      <c r="B1741" s="5"/>
-      <c r="C1741" s="7"/>
-      <c r="D1741" s="7"/>
-    </row>
-    <row r="1742" spans="1:4">
-      <c r="A1742" s="4"/>
-      <c r="B1742" s="5"/>
-      <c r="C1742" s="7"/>
-      <c r="D1742" s="7"/>
-    </row>
-    <row r="1743" spans="1:4">
-      <c r="A1743" s="4"/>
-      <c r="B1743" s="5"/>
-      <c r="C1743" s="7"/>
-      <c r="D1743" s="7"/>
-    </row>
-    <row r="1744" spans="1:4">
-      <c r="A1744" s="4"/>
-      <c r="B1744" s="5"/>
-      <c r="C1744" s="7"/>
-      <c r="D1744" s="7"/>
-    </row>
-    <row r="1745" spans="1:2">
-      <c r="A1745" s="4"/>
-      <c r="B1745" s="5"/>
-    </row>
-    <row r="1746" spans="1:2">
-      <c r="A1746" s="4"/>
-      <c r="B1746" s="5"/>
-    </row>
-    <row r="1747" spans="1:2">
-      <c r="A1747" s="4"/>
-      <c r="B1747" s="5"/>
-    </row>
-    <row r="1748" spans="1:2">
-      <c r="A1748" s="4"/>
-      <c r="B1748" s="5"/>
-    </row>
-    <row r="1749" spans="1:2">
-      <c r="A1749" s="4"/>
-      <c r="B1749" s="5"/>
-    </row>
-    <row r="1750" spans="1:2">
-      <c r="A1750" s="4"/>
-      <c r="B1750" s="5"/>
-    </row>
-    <row r="1751" spans="1:2">
-      <c r="A1751" s="4"/>
-      <c r="B1751" s="5"/>
-    </row>
-    <row r="1752" spans="1:2">
-      <c r="A1752" s="4"/>
-      <c r="B1752" s="5"/>
-    </row>
-    <row r="1753" spans="1:2">
-      <c r="A1753" s="4"/>
-      <c r="B1753" s="5"/>
-    </row>
-    <row r="1754" spans="1:2">
-      <c r="A1754" s="4"/>
-      <c r="B1754" s="5"/>
-    </row>
-    <row r="1755" spans="1:2">
-      <c r="A1755" s="4"/>
-      <c r="B1755" s="5"/>
-    </row>
-    <row r="1756" spans="1:2">
-      <c r="A1756" s="4"/>
-      <c r="B1756" s="5"/>
-    </row>
-    <row r="1757" spans="1:2">
-      <c r="A1757" s="4"/>
-      <c r="B1757" s="5"/>
-    </row>
-    <row r="1758" spans="1:2">
-      <c r="A1758" s="4"/>
-      <c r="B1758" s="5"/>
-    </row>
-    <row r="1759" spans="1:2">
-      <c r="A1759" s="4"/>
-      <c r="B1759" s="5"/>
-    </row>
-    <row r="1760" spans="1:2">
-      <c r="A1760" s="4"/>
-      <c r="B1760" s="5"/>
-    </row>
-    <row r="1761" spans="1:2">
-      <c r="A1761" s="4"/>
-      <c r="B1761" s="5"/>
-    </row>
-    <row r="1762" spans="1:2">
-      <c r="A1762" s="4"/>
-      <c r="B1762" s="5"/>
-    </row>
-    <row r="1763" spans="1:3">
-      <c r="A1763" s="1">
+    <row r="1720" spans="1:3">
+      <c r="A1720" s="1">
         <v>46280</v>
       </c>
-      <c r="B1763" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1763">
+      <c r="B1720" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1720">
         <v>567696</v>
       </c>
     </row>
-    <row r="1764" spans="1:3">
-      <c r="A1764" s="1">
+    <row r="1721" spans="1:3">
+      <c r="A1721" s="1">
         <v>46281</v>
       </c>
-      <c r="B1764" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1764">
+      <c r="B1721" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1721">
         <v>1093962</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1763">
+  <autoFilter ref="A1:E1721">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B1270 B1272:B1302 B1304:B1334 B1336:B1366 B1368:B1398 B1400:B1430 B1432:B1493 B1495:B1524 B1526:B1555 B1557:B1587 B1589:B1619 B1621:B1651 B1653:B1682 B1684:B1713 B1715:B1730 B1732:B1762">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B1270 B1272:B1302 B1304:B1334 B1336:B1366 B1368:B1398 B1400:B1430 B1432:B1493 B1495:B1524 B1526:B1555 B1557:B1587 B1589:B1619 B1621:B1651 B1653:B1682 B1684:B1713 B1715:B1719">
       <formula1>店舗マスタ!$A$2:$A$31</formula1>
     </dataValidation>
   </dataValidations>

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1721</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,15 +204,38 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,9 +249,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -236,6 +258,37 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,15 +302,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,44 +318,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,30 +326,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +422,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,91 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -580,6 +580,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -587,6 +602,30 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -602,21 +641,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,32 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1722"/>
+  <dimension ref="A1:E1723"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23201,8 +23201,19 @@
         <v>1912203</v>
       </c>
     </row>
+    <row r="1723" spans="1:3">
+      <c r="A1723" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1723">
+        <v>796299</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1721">
+  <autoFilter ref="A1:E1722">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1722</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1769" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,17 +203,23 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,9 +232,86 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,21 +326,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,76 +334,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,43 +374,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +398,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,19 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,7 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,19 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,7 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,26 +571,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -607,16 +607,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,26 +654,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1723"/>
+  <dimension ref="A1:E1724"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23212,8 +23212,19 @@
         <v>796299</v>
       </c>
     </row>
+    <row r="1724" spans="1:3">
+      <c r="A1724" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1724">
+        <v>1042455</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1722">
+  <autoFilter ref="A1:E1723">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1723</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,50 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -264,16 +220,37 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,8 +272,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,24 +317,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,31 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,13 +380,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,13 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,7 +440,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,25 +506,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,49 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,45 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -588,15 +627,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -607,16 +637,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -638,197 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1724"/>
+  <dimension ref="A1:E1725"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23223,8 +23223,19 @@
         <v>1042455</v>
       </c>
     </row>
+    <row r="1725" spans="1:3">
+      <c r="A1725" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1725">
+        <v>2718679</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1723">
+  <autoFilter ref="A1:E1724">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1724</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,75 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -289,6 +220,65 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -302,8 +292,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,7 +317,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -339,13 +346,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -362,6 +362,96 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -374,13 +464,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,25 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,49 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,19 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,49 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,17 +640,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,35 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1725"/>
+  <dimension ref="A1:E1726"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23234,8 +23234,19 @@
         <v>2718679</v>
       </c>
     </row>
+    <row r="1726" spans="1:3">
+      <c r="A1726" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1726">
+        <v>1372540</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1724">
+  <autoFilter ref="A1:E1725">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1725</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,29 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -233,8 +210,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,7 +234,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,29 +248,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -292,11 +255,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -317,18 +279,18 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -340,10 +302,48 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,31 +494,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,61 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,15 +610,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -621,30 +621,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,154 +644,178 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1726"/>
+  <dimension ref="A1:E1727"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23245,8 +23245,19 @@
         <v>1372540</v>
       </c>
     </row>
+    <row r="1727" spans="1:3">
+      <c r="A1727" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1727">
+        <v>495306</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1725">
+  <autoFilter ref="A1:E1726">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1726</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,24 +203,16 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,14 +234,30 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,7 +272,44 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,54 +331,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +386,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +434,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,19 +470,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,37 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,13 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +518,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,21 +601,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -621,35 +612,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,167 +630,205 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1727"/>
+  <dimension ref="A1:E1728"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23256,8 +23256,19 @@
         <v>495306</v>
       </c>
     </row>
+    <row r="1728" spans="1:3">
+      <c r="A1728" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1728">
+        <v>11631111</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1726">
+  <autoFilter ref="A1:E1727">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1727</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1774" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,23 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,18 +218,49 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -256,46 +272,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -315,19 +301,34 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -339,11 +340,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -368,6 +368,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -380,7 +404,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,25 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,37 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +458,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,37 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,7 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,36 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,8 +613,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -649,11 +643,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,152 +683,152 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1728"/>
+  <dimension ref="A1:E1729"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23267,8 +23267,19 @@
         <v>11631111</v>
       </c>
     </row>
+    <row r="1729" spans="1:3">
+      <c r="A1729" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1729">
+        <v>600414</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1727">
+  <autoFilter ref="A1:E1728">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1728</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1775" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,6 +204,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -217,17 +232,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -237,14 +243,6 @@
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -272,18 +270,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -301,9 +292,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,22 +302,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,8 +316,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,85 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +440,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +476,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,15 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -636,6 +627,26 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
@@ -657,36 +668,25 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,140 +695,140 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1729"/>
+  <dimension ref="A1:E1730"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23278,8 +23278,19 @@
         <v>600414</v>
       </c>
     </row>
+    <row r="1730" spans="1:3">
+      <c r="A1730" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1730">
+        <v>680147</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1728">
+  <autoFilter ref="A1:E1729">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1729</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1730</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,52 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,23 +227,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -300,9 +257,60 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,18 +325,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -340,10 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,67 +464,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,25 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,19 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,8 +619,37 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -624,66 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,130 +692,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1730"/>
+  <dimension ref="A1:E1731"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23289,8 +23289,19 @@
         <v>680147</v>
       </c>
     </row>
+    <row r="1731" spans="1:3">
+      <c r="A1731" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1731">
+        <v>1336609</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1729">
+  <autoFilter ref="A1:E1730">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1730</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1731</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,60 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,43 +278,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -273,37 +287,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,18 +316,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +422,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,109 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,13 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -618,33 +612,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -668,167 +635,200 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1731"/>
+  <dimension ref="A1:E1732"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23300,8 +23300,19 @@
         <v>1336609</v>
       </c>
     </row>
+    <row r="1732" spans="1:3">
+      <c r="A1732" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1732">
+        <v>2716675</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1730">
+  <autoFilter ref="A1:E1731">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1731</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,14 +204,45 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,14 +257,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,52 +266,6 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -308,6 +286,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -317,17 +302,18 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -341,7 +327,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +398,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,43 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,7 +440,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,31 +464,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,19 +506,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,13 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -591,6 +582,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,6 +627,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -640,7 +655,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -649,22 +664,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1732"/>
+  <dimension ref="A1:E1733"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23311,8 +23311,19 @@
         <v>2716675</v>
       </c>
     </row>
+    <row r="1733" spans="1:3">
+      <c r="A1733" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1733">
+        <v>1270120</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1731">
+  <autoFilter ref="A1:E1732">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1732</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1779" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,7 +218,15 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -240,14 +248,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -257,22 +257,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,15 +272,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,15 +294,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -334,14 +325,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,31 +404,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +452,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,37 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,19 +500,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,13 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -586,17 +610,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,26 +632,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,8 +654,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -664,7 +664,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,19 +674,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,127 +695,127 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1733"/>
+  <dimension ref="A1:E1734"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23322,8 +23322,19 @@
         <v>1270120</v>
       </c>
     </row>
+    <row r="1734" spans="1:3">
+      <c r="A1734" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1734">
+        <v>587195</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1732">
+  <autoFilter ref="A1:E1733">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1733</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1734</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1780" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,8 +166,8 @@
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
@@ -203,33 +203,11 @@
       <charset val="128"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -248,6 +226,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -257,17 +257,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -286,16 +286,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,13 +318,6 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -331,17 +332,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,37 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,37 +374,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,19 +404,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,13 +440,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,13 +476,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,19 +512,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,30 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -612,10 +588,8 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -632,6 +606,26 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +648,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,127 +695,127 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1734"/>
+  <dimension ref="A1:E1735"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23333,8 +23333,16 @@
         <v>587195</v>
       </c>
     </row>
+    <row r="1735" spans="1:2">
+      <c r="A1735" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1733">
+  <autoFilter ref="A1:E1734">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1735</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1782" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,61 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,25 +271,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -255,6 +302,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -264,23 +318,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,37 +333,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -333,17 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,31 +464,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,79 +506,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,49 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,56 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,45 +654,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -657,36 +668,25 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,140 +695,140 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="26" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1736"/>
+  <dimension ref="A1:E1737"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23355,8 +23355,19 @@
         <v>2746814</v>
       </c>
     </row>
+    <row r="1737" spans="1:3">
+      <c r="A1737" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1737">
+        <v>734242</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1735">
+  <autoFilter ref="A1:E1736">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1736</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,39 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,23 +227,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,8 +272,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,23 +294,39 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -339,11 +340,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,19 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +398,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,19 +422,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,7 +494,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,13 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,85 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -601,7 +590,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,11 +610,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,17 +634,22 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1737"/>
+  <dimension ref="A1:E1738"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23366,8 +23366,19 @@
         <v>734242</v>
       </c>
     </row>
+    <row r="1738" spans="1:3">
+      <c r="A1738" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1738">
+        <v>7510170</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1736">
+  <autoFilter ref="A1:E1737">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1737</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1784" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,16 +203,48 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,23 +266,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,14 +295,6 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -281,7 +303,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,39 +332,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +386,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,157 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,75 +571,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -668,167 +603,232 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1738"/>
+  <dimension ref="A1:E1739"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23377,8 +23377,19 @@
         <v>7510170</v>
       </c>
     </row>
+    <row r="1739" spans="1:3">
+      <c r="A1739" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1739">
+        <v>1492689</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1737">
+  <autoFilter ref="A1:E1738">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1738</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1785" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
@@ -203,16 +203,83 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -227,8 +294,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -236,7 +318,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -253,88 +335,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +434,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,25 +470,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,13 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,91 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,26 +612,33 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -647,24 +660,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1739"/>
+  <dimension ref="A1:E1740"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23388,8 +23388,19 @@
         <v>1492689</v>
       </c>
     </row>
+    <row r="1740" spans="1:3">
+      <c r="A1740" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1740">
+        <v>1032047</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1738">
+  <autoFilter ref="A1:E1739">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1739</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1786" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,13 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -218,7 +211,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,9 +241,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -259,6 +252,14 @@
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -272,7 +273,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,6 +294,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -295,22 +317,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -325,18 +333,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,31 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +392,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,25 +422,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,103 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,15 +586,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -614,7 +605,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,8 +628,28 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -657,36 +668,25 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,127 +695,127 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1740"/>
+  <dimension ref="A1:E1741"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23399,8 +23399,19 @@
         <v>1032047</v>
       </c>
     </row>
+    <row r="1741" spans="1:3">
+      <c r="A1741" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1741">
+        <v>799893</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1739">
+  <autoFilter ref="A1:E1740">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1740</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,21 @@
       <charset val="128"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -217,6 +232,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -224,9 +263,54 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -247,45 +331,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -294,54 +339,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,25 +362,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,61 +500,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,85 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,17 +586,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,15 +624,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -645,11 +632,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1741"/>
+  <dimension ref="A1:E1742"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23410,8 +23410,19 @@
         <v>799893</v>
       </c>
     </row>
+    <row r="1742" spans="1:3">
+      <c r="A1742" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1742">
+        <v>978918</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1740">
+  <autoFilter ref="A1:E1741">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1741</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1788" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,38 +203,16 @@
       <charset val="128"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,6 +235,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -264,15 +249,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -286,8 +263,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,6 +279,28 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -309,15 +309,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -331,17 +333,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,31 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,37 +392,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +410,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,7 +428,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,19 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,31 +500,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,11 +591,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,11 +630,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,148 +674,148 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1742"/>
+  <dimension ref="A1:E1743"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23421,8 +23421,19 @@
         <v>978918</v>
       </c>
     </row>
+    <row r="1743" spans="1:3">
+      <c r="A1743" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1743">
+        <v>727607</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1741">
+  <autoFilter ref="A1:E1742">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1742</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,37 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -241,15 +210,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,6 +233,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -271,9 +255,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,6 +276,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -302,7 +293,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -318,8 +309,16 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -327,7 +326,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,8 +339,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +494,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,31 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,115 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,26 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,6 +610,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -641,6 +639,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,176 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1743"/>
+  <dimension ref="A1:E1744"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23432,8 +23432,19 @@
         <v>727607</v>
       </c>
     </row>
+    <row r="1744" spans="1:3">
+      <c r="A1744" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1744">
+        <v>599997</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1742">
+  <autoFilter ref="A1:E1743">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1743</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1790" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,81 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -294,25 +221,89 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -332,10 +323,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,55 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,25 +392,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +476,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,55 +518,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,33 +595,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -639,6 +606,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1744"/>
+  <dimension ref="A1:E1745"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23443,8 +23443,19 @@
         <v>599997</v>
       </c>
     </row>
+    <row r="1745" spans="1:3">
+      <c r="A1745" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1745">
+        <v>955088</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1743">
+  <autoFilter ref="A1:E1744">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1744</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,35 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -211,9 +240,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,47 +270,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -301,7 +294,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,23 +324,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -342,6 +334,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -358,6 +358,72 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF4E79A7"/>
         <bgColor rgb="FF4E79A7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -380,43 +446,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,43 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,31 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +500,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -596,6 +596,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -615,21 +630,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1745"/>
+  <dimension ref="A1:E1746"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23454,8 +23454,19 @@
         <v>955088</v>
       </c>
     </row>
+    <row r="1746" spans="1:3">
+      <c r="A1746" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1746">
+        <v>1488093</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1744">
+  <autoFilter ref="A1:E1745">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1745</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -217,15 +217,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -240,24 +248,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,21 +265,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,22 +279,29 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,10 +316,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -339,11 +331,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +440,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,43 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,55 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,25 +482,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +506,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,23 +574,17 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -611,25 +605,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,6 +639,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1746"/>
+  <dimension ref="A1:E1747"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23465,8 +23465,19 @@
         <v>1488093</v>
       </c>
     </row>
+    <row r="1747" spans="1:3">
+      <c r="A1747" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1747">
+        <v>509377</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1745">
+  <autoFilter ref="A1:E1746">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1746</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1793" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,13 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -225,6 +218,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -233,15 +249,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -249,7 +257,37 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,62 +302,32 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -333,17 +341,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +416,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,49 +494,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,85 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,17 +574,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -600,6 +591,30 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -623,33 +638,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,25 +657,36 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,127 +695,127 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1747"/>
+  <dimension ref="A1:E1748"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23476,8 +23476,19 @@
         <v>509377</v>
       </c>
     </row>
+    <row r="1748" spans="1:3">
+      <c r="A1748" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1748">
+        <v>509377</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1746">
+  <autoFilter ref="A1:E1747">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1747</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,15 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,6 +218,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -234,7 +256,60 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,65 +331,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -323,25 +339,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,18 +362,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -386,13 +374,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +398,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +428,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,103 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,46 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -598,23 +633,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,15 +654,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -657,105 +668,91 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -764,58 +761,61 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1748"/>
+  <dimension ref="A1:E1749"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23487,8 +23487,19 @@
         <v>509377</v>
       </c>
     </row>
+    <row r="1749" spans="1:3">
+      <c r="A1749" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1749">
+        <v>6486118</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1747">
+  <autoFilter ref="A1:E1748">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1748</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,23 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,36 +218,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,7 +235,61 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -299,9 +310,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,34 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,25 +386,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,19 +410,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,37 +428,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,49 +446,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,7 +482,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -588,20 +599,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -626,15 +626,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,167 +659,176 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1749"/>
+  <dimension ref="A1:E1750"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23498,8 +23498,19 @@
         <v>6486118</v>
       </c>
     </row>
+    <row r="1750" spans="1:3">
+      <c r="A1750" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1750">
+        <v>685278</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1748">
+  <autoFilter ref="A1:E1749">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1749</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1750</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1796" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,10 +203,11 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -215,45 +216,6 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -271,8 +233,92 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -287,38 +333,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -328,22 +344,6 @@
       <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +440,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +464,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +476,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,61 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,25 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -578,39 +578,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,6 +630,39 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1750"/>
+  <dimension ref="A1:E1751"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23509,8 +23509,19 @@
         <v>685278</v>
       </c>
     </row>
+    <row r="1751" spans="1:3">
+      <c r="A1751" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1751">
+        <v>814292</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1749">
+  <autoFilter ref="A1:E1750">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1750</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1797" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,6 +204,29 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -211,9 +234,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,15 +248,62 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,15 +318,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -274,67 +335,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,31 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,133 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,11 +573,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,41 +610,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,8 +636,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -663,8 +648,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1751"/>
+  <dimension ref="A1:E1752"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23520,8 +23520,19 @@
         <v>814292</v>
       </c>
     </row>
+    <row r="1752" spans="1:3">
+      <c r="A1752" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1752">
+        <v>858924</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1750">
+  <autoFilter ref="A1:E1751">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1751</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
@@ -203,11 +203,63 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -220,7 +272,38 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -235,75 +318,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,31 +339,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,25 +422,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,19 +470,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,55 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,19 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,6 +601,44 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -606,15 +650,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,57 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,143 +692,143 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1752"/>
+  <dimension ref="A1:E1754"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23531,8 +23531,30 @@
         <v>858924</v>
       </c>
     </row>
+    <row r="1753" spans="1:3">
+      <c r="A1753" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1753">
+        <v>858924</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:3">
+      <c r="A1754" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1754">
+        <v>788203</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1751">
+  <autoFilter ref="A1:E1753">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1753</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,21 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -226,7 +211,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -240,8 +225,46 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -257,20 +280,43 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -288,60 +334,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +464,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,79 +494,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,13 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,37 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,61 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -603,35 +647,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
@@ -639,31 +654,16 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -674,148 +674,148 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1754"/>
+  <dimension ref="A1:E1755"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23553,8 +23553,19 @@
         <v>788203</v>
       </c>
     </row>
+    <row r="1755" spans="1:3">
+      <c r="A1755" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1755">
+        <v>1473181</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1753">
+  <autoFilter ref="A1:E1754">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1754</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -167,8 +167,8 @@
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,16 +210,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,75 +220,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,7 +234,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,6 +255,67 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -332,18 +324,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -368,13 +368,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +398,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,85 +506,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,13 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -600,8 +604,43 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -624,47 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,130 +692,130 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1755"/>
+  <dimension ref="A1:E1756"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23564,8 +23564,19 @@
         <v>1473181</v>
       </c>
     </row>
+    <row r="1756" spans="1:3">
+      <c r="A1756" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1756">
+        <v>523130</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1754">
+  <autoFilter ref="A1:E1755">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1755</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1802" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,9 +210,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,6 +219,50 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,15 +276,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,14 +286,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,46 +308,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -333,17 +333,17 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +398,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +416,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,25 +512,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,103 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,21 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -604,28 +589,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,16 +625,36 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -663,8 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,19 +674,19 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,97 +695,97 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -794,41 +794,41 @@
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1756"/>
+  <dimension ref="A1:E1757"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23575,8 +23575,19 @@
         <v>523130</v>
       </c>
     </row>
+    <row r="1757" spans="1:3">
+      <c r="A1757" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1757">
+        <v>435617</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1755">
+  <autoFilter ref="A1:E1756">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1756</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1803" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,8 +203,24 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,14 +234,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -238,31 +247,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -276,17 +263,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,6 +294,21 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -310,7 +317,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -324,24 +331,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +488,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,97 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,55 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -589,58 +589,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,8 +613,58 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,148 +674,148 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1757"/>
+  <dimension ref="A1:E1758"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23586,8 +23586,19 @@
         <v>435617</v>
       </c>
     </row>
+    <row r="1758" spans="1:3">
+      <c r="A1758" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1758">
+        <v>679314</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1756">
+  <autoFilter ref="A1:E1757">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1757</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1758</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,23 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -219,8 +234,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,6 +263,37 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -240,8 +301,31 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,90 +346,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="34">
     <fill>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +386,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,7 +398,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,85 +446,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,13 +470,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,30 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -595,6 +619,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -606,15 +650,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -633,48 +668,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,152 +683,152 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1758"/>
+  <dimension ref="A1:E1759"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23597,8 +23597,19 @@
         <v>679314</v>
       </c>
     </row>
+    <row r="1759" spans="1:3">
+      <c r="A1759" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1759">
+        <v>497131</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1757">
+  <autoFilter ref="A1:E1758">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1758</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,6 +210,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -219,10 +249,77 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -242,105 +339,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,25 +386,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +440,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,67 +476,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,25 +524,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,32 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -590,22 +616,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,26 +641,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1759"/>
+  <dimension ref="A1:E1760"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23608,8 +23608,19 @@
         <v>497131</v>
       </c>
     </row>
+    <row r="1760" spans="1:3">
+      <c r="A1760" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1760">
+        <v>6316870</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1758">
+  <autoFilter ref="A1:E1759">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1759</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1806" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,6 +210,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -218,8 +226,47 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,54 +295,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -308,6 +309,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -315,9 +324,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,15 +340,7 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +380,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,31 +452,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,19 +476,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,31 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,6 +606,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,50 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,152 +683,152 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1760"/>
+  <dimension ref="A1:E1762"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23619,8 +23619,30 @@
         <v>6316870</v>
       </c>
     </row>
+    <row r="1761" spans="1:3">
+      <c r="A1761" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1761">
+        <v>6316870</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:3">
+      <c r="A1762" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1762">
+        <v>632989</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1759">
+  <autoFilter ref="A1:E1761">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1761</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1808" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,10 +203,85 @@
       <charset val="128"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -226,47 +301,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,23 +317,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,40 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +404,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,163 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,30 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -627,10 +603,41 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -653,18 +660,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1762"/>
+  <dimension ref="A1:E1763"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23641,8 +23641,19 @@
         <v>632989</v>
       </c>
     </row>
+    <row r="1763" spans="1:3">
+      <c r="A1763" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1763">
+        <v>1556330</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1761">
+  <autoFilter ref="A1:E1762">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1762</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1809" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,21 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -235,14 +220,23 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,6 +249,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -262,8 +271,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,7 +281,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,17 +303,22 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,34 +331,19 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,12 +362,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -380,7 +374,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,19 +452,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,43 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,85 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,21 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -603,9 +588,50 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -629,7 +655,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,34 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1763"/>
+  <dimension ref="A1:E1764"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23652,8 +23652,19 @@
         <v>1556330</v>
       </c>
     </row>
+    <row r="1764" spans="1:3">
+      <c r="A1764" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1764">
+        <v>655058</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1762">
+  <autoFilter ref="A1:E1763">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1763</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,114 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,68 +325,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -296,54 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +398,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,151 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,17 +586,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -629,9 +618,20 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,8 +654,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,8 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,152 +683,152 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1764"/>
+  <dimension ref="A1:E1765"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23663,8 +23663,19 @@
         <v>655058</v>
       </c>
     </row>
+    <row r="1765" spans="1:3">
+      <c r="A1765" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1765">
+        <v>446770</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1763">
+  <autoFilter ref="A1:E1764">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1764</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1811" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,36 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,15 +247,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,10 +264,47 @@
     </font>
     <font>
       <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -272,74 +332,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -362,7 +362,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,163 +464,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -543,6 +483,66 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,6 +567,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,26 +625,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -654,8 +643,19 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,8 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1765"/>
+  <dimension ref="A1:E1766"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23674,8 +23674,19 @@
         <v>446770</v>
       </c>
     </row>
+    <row r="1766" spans="1:3">
+      <c r="A1766" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1766">
+        <v>544719</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1764">
+  <autoFilter ref="A1:E1765">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1765</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1766</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,36 +204,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,8 +235,29 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,11 +271,42 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -287,46 +318,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +341,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,19 +362,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +434,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,103 +476,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +512,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,15 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -606,6 +597,24 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -644,7 +653,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,176 +668,167 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1766"/>
+  <dimension ref="A1:E1767"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23685,8 +23685,19 @@
         <v>544719</v>
       </c>
     </row>
+    <row r="1767" spans="1:3">
+      <c r="A1767" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1767">
+        <v>808908</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1765">
+  <autoFilter ref="A1:E1766">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/auPAY1.xlsx
+++ b/dashboard/data/incoming/auPAY1.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1766</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$1767</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1813" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1814" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,16 +203,30 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,14 +241,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -243,7 +249,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,7 +278,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,6 +307,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -280,23 +325,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,38 +339,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +392,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,157 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,11 +601,35 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,30 +658,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -674,161 +674,161 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="38" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1491,7 +1491,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1767"/>
+  <dimension ref="A1:E1768"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -23696,8 +23696,19 @@
         <v>808908</v>
       </c>
     </row>
+    <row r="1768" spans="1:3">
+      <c r="A1768" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1768">
+        <v>723256</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E1766">
+  <autoFilter ref="A1:E1767">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
